--- a/artfynd/A 32783-2022 artfynd.xlsx
+++ b/artfynd/A 32783-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32783-2022 artfynd.xlsx
+++ b/artfynd/A 32783-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149426</v>
+        <v>121149424</v>
       </c>
       <c r="B4" t="n">
-        <v>78335</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532833</v>
+        <v>532834</v>
       </c>
       <c r="R4" t="n">
-        <v>6872863</v>
+        <v>6872866</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149425</v>
+        <v>121149423</v>
       </c>
       <c r="B5" t="n">
-        <v>78243</v>
+        <v>91973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532835</v>
+        <v>532829</v>
       </c>
       <c r="R5" t="n">
-        <v>6872853</v>
+        <v>6872946</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149424</v>
+        <v>121149425</v>
       </c>
       <c r="B6" t="n">
-        <v>78334</v>
+        <v>78246</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532834</v>
+        <v>532835</v>
       </c>
       <c r="R6" t="n">
-        <v>6872866</v>
+        <v>6872853</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1235,7 @@
         <v>121149421</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121149423</v>
+        <v>121149422</v>
       </c>
       <c r="B8" t="n">
-        <v>91963</v>
+        <v>91985</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532829</v>
+        <v>532854</v>
       </c>
       <c r="R8" t="n">
-        <v>6872946</v>
+        <v>6872868</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121149422</v>
+        <v>121149426</v>
       </c>
       <c r="B9" t="n">
-        <v>91975</v>
+        <v>78338</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,25 +1466,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532854</v>
+        <v>532833</v>
       </c>
       <c r="R9" t="n">
-        <v>6872868</v>
+        <v>6872863</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 32783-2022 artfynd.xlsx
+++ b/artfynd/A 32783-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149424</v>
+        <v>121149426</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>78338</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532834</v>
+        <v>532833</v>
       </c>
       <c r="R4" t="n">
-        <v>6872866</v>
+        <v>6872863</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149423</v>
+        <v>121149421</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532829</v>
+        <v>532654</v>
       </c>
       <c r="R5" t="n">
-        <v>6872946</v>
+        <v>6872893</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149425</v>
+        <v>121149422</v>
       </c>
       <c r="B6" t="n">
-        <v>78246</v>
+        <v>91985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,25 +1133,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532835</v>
+        <v>532854</v>
       </c>
       <c r="R6" t="n">
-        <v>6872853</v>
+        <v>6872868</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121149421</v>
+        <v>121149423</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>91973</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1244,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532654</v>
+        <v>532829</v>
       </c>
       <c r="R7" t="n">
-        <v>6872893</v>
+        <v>6872946</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121149422</v>
+        <v>121149425</v>
       </c>
       <c r="B8" t="n">
-        <v>91985</v>
+        <v>78246</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,25 +1355,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532854</v>
+        <v>532835</v>
       </c>
       <c r="R8" t="n">
-        <v>6872868</v>
+        <v>6872853</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121149426</v>
+        <v>121149424</v>
       </c>
       <c r="B9" t="n">
-        <v>78338</v>
+        <v>78337</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532833</v>
+        <v>532834</v>
       </c>
       <c r="R9" t="n">
-        <v>6872863</v>
+        <v>6872866</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 32783-2022 artfynd.xlsx
+++ b/artfynd/A 32783-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149426</v>
+        <v>121149422</v>
       </c>
       <c r="B4" t="n">
-        <v>78338</v>
+        <v>91997</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532833</v>
+        <v>532854</v>
       </c>
       <c r="R4" t="n">
-        <v>6872863</v>
+        <v>6872868</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149421</v>
+        <v>121149425</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>78249</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532654</v>
+        <v>532835</v>
       </c>
       <c r="R5" t="n">
-        <v>6872893</v>
+        <v>6872853</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149422</v>
+        <v>121149423</v>
       </c>
       <c r="B6" t="n">
         <v>91985</v>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532854</v>
+        <v>532829</v>
       </c>
       <c r="R6" t="n">
-        <v>6872868</v>
+        <v>6872946</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121149423</v>
+        <v>121149421</v>
       </c>
       <c r="B7" t="n">
-        <v>91973</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1244,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532829</v>
+        <v>532654</v>
       </c>
       <c r="R7" t="n">
-        <v>6872946</v>
+        <v>6872893</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121149425</v>
+        <v>121149426</v>
       </c>
       <c r="B8" t="n">
-        <v>78246</v>
+        <v>78341</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532835</v>
+        <v>532833</v>
       </c>
       <c r="R8" t="n">
-        <v>6872853</v>
+        <v>6872863</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,7 +1457,7 @@
         <v>121149424</v>
       </c>
       <c r="B9" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 32783-2022 artfynd.xlsx
+++ b/artfynd/A 32783-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149422</v>
+        <v>121149421</v>
       </c>
       <c r="B4" t="n">
-        <v>91997</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532854</v>
+        <v>532654</v>
       </c>
       <c r="R4" t="n">
-        <v>6872868</v>
+        <v>6872893</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149425</v>
+        <v>121149424</v>
       </c>
       <c r="B5" t="n">
-        <v>78249</v>
+        <v>78340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532835</v>
+        <v>532834</v>
       </c>
       <c r="R5" t="n">
-        <v>6872853</v>
+        <v>6872866</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149423</v>
+        <v>121149422</v>
       </c>
       <c r="B6" t="n">
-        <v>91985</v>
+        <v>91998</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532829</v>
+        <v>532854</v>
       </c>
       <c r="R6" t="n">
-        <v>6872946</v>
+        <v>6872868</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121149421</v>
+        <v>121149426</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532654</v>
+        <v>532833</v>
       </c>
       <c r="R7" t="n">
-        <v>6872893</v>
+        <v>6872863</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121149426</v>
+        <v>121149423</v>
       </c>
       <c r="B8" t="n">
-        <v>78341</v>
+        <v>91986</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,25 +1355,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532833</v>
+        <v>532829</v>
       </c>
       <c r="R8" t="n">
-        <v>6872863</v>
+        <v>6872946</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121149424</v>
+        <v>121149425</v>
       </c>
       <c r="B9" t="n">
-        <v>78340</v>
+        <v>78249</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532834</v>
+        <v>532835</v>
       </c>
       <c r="R9" t="n">
-        <v>6872866</v>
+        <v>6872853</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 32783-2022 artfynd.xlsx
+++ b/artfynd/A 32783-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149421</v>
+        <v>121149422</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>92001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532654</v>
+        <v>532854</v>
       </c>
       <c r="R4" t="n">
-        <v>6872893</v>
+        <v>6872868</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149424</v>
+        <v>121149426</v>
       </c>
       <c r="B5" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532834</v>
+        <v>532833</v>
       </c>
       <c r="R5" t="n">
-        <v>6872866</v>
+        <v>6872863</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149422</v>
+        <v>121149423</v>
       </c>
       <c r="B6" t="n">
-        <v>91998</v>
+        <v>91989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532854</v>
+        <v>532829</v>
       </c>
       <c r="R6" t="n">
-        <v>6872868</v>
+        <v>6872946</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121149426</v>
+        <v>121149421</v>
       </c>
       <c r="B7" t="n">
-        <v>78341</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532833</v>
+        <v>532654</v>
       </c>
       <c r="R7" t="n">
-        <v>6872863</v>
+        <v>6872893</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121149423</v>
+        <v>121149425</v>
       </c>
       <c r="B8" t="n">
-        <v>91986</v>
+        <v>78252</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,25 +1355,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532829</v>
+        <v>532835</v>
       </c>
       <c r="R8" t="n">
-        <v>6872946</v>
+        <v>6872853</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121149425</v>
+        <v>121149424</v>
       </c>
       <c r="B9" t="n">
-        <v>78249</v>
+        <v>78343</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532835</v>
+        <v>532834</v>
       </c>
       <c r="R9" t="n">
-        <v>6872853</v>
+        <v>6872866</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 32783-2022 artfynd.xlsx
+++ b/artfynd/A 32783-2022 artfynd.xlsx
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149426</v>
+        <v>121149423</v>
       </c>
       <c r="B5" t="n">
-        <v>78344</v>
+        <v>91989</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532833</v>
+        <v>532829</v>
       </c>
       <c r="R5" t="n">
-        <v>6872863</v>
+        <v>6872946</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149423</v>
+        <v>121149425</v>
       </c>
       <c r="B6" t="n">
-        <v>91989</v>
+        <v>78252</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,25 +1133,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532829</v>
+        <v>532835</v>
       </c>
       <c r="R6" t="n">
-        <v>6872946</v>
+        <v>6872853</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121149421</v>
+        <v>121149424</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532654</v>
+        <v>532834</v>
       </c>
       <c r="R7" t="n">
-        <v>6872893</v>
+        <v>6872866</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121149425</v>
+        <v>121149421</v>
       </c>
       <c r="B8" t="n">
-        <v>78252</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532835</v>
+        <v>532654</v>
       </c>
       <c r="R8" t="n">
-        <v>6872853</v>
+        <v>6872893</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121149424</v>
+        <v>121149426</v>
       </c>
       <c r="B9" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532834</v>
+        <v>532833</v>
       </c>
       <c r="R9" t="n">
-        <v>6872866</v>
+        <v>6872863</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 32783-2022 artfynd.xlsx
+++ b/artfynd/A 32783-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112607080</v>
+        <v>121149422</v>
       </c>
       <c r="B3" t="n">
-        <v>91044</v>
+        <v>92001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,20 +825,24 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skålvallen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532622</v>
+        <v>532854</v>
       </c>
       <c r="R3" t="n">
-        <v>6873247</v>
+        <v>6872868</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,17 +866,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149422</v>
+        <v>121149423</v>
       </c>
       <c r="B4" t="n">
-        <v>92001</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532854</v>
+        <v>532829</v>
       </c>
       <c r="R4" t="n">
-        <v>6872868</v>
+        <v>6872946</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149423</v>
+        <v>121149425</v>
       </c>
       <c r="B5" t="n">
-        <v>91989</v>
+        <v>78252</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1026,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532829</v>
+        <v>532835</v>
       </c>
       <c r="R5" t="n">
-        <v>6872946</v>
+        <v>6872853</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149425</v>
+        <v>121149424</v>
       </c>
       <c r="B6" t="n">
-        <v>78252</v>
+        <v>78343</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532835</v>
+        <v>532834</v>
       </c>
       <c r="R6" t="n">
-        <v>6872853</v>
+        <v>6872866</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121149424</v>
+        <v>121149421</v>
       </c>
       <c r="B7" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1276,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532834</v>
+        <v>532654</v>
       </c>
       <c r="R7" t="n">
-        <v>6872866</v>
+        <v>6872893</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121149421</v>
+        <v>121149426</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1387,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532654</v>
+        <v>532833</v>
       </c>
       <c r="R8" t="n">
-        <v>6872893</v>
+        <v>6872863</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,117 +1455,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>121149426</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78344</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Skålvallen, Hls</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>532833</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6872863</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Färila</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32783-2022 artfynd.xlsx
+++ b/artfynd/A 32783-2022 artfynd.xlsx
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104160569</v>
+        <v>121149425</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skålvallen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532621.6674600595</v>
+        <v>532835</v>
       </c>
       <c r="R2" t="n">
-        <v>6873246.587465568</v>
+        <v>6872853</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149422</v>
+        <v>121149423</v>
       </c>
       <c r="B3" t="n">
-        <v>92001</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532854</v>
+        <v>532829</v>
       </c>
       <c r="R3" t="n">
-        <v>6872868</v>
+        <v>6872946</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,57 +887,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149423</v>
+        <v>112607080</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skålvallen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532829</v>
+        <v>532622</v>
       </c>
       <c r="R4" t="n">
-        <v>6872946</v>
+        <v>6873247</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,17 +952,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149425</v>
+        <v>121149422</v>
       </c>
       <c r="B5" t="n">
-        <v>78252</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532835</v>
+        <v>532854</v>
       </c>
       <c r="R5" t="n">
-        <v>6872853</v>
+        <v>6872868</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1125,37 +1095,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149424</v>
+        <v>121149421</v>
       </c>
       <c r="B6" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1169,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532834</v>
+        <v>532654</v>
       </c>
       <c r="R6" t="n">
-        <v>6872866</v>
+        <v>6872893</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1236,15 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121149421</v>
+        <v>121149424</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,21 +1212,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1280,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532654</v>
+        <v>532834</v>
       </c>
       <c r="R7" t="n">
-        <v>6872893</v>
+        <v>6872866</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1350,12 +1310,7 @@
         <v>121149426</v>
       </c>
       <c r="B8" t="n">
-        <v>78344</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32783-2022 artfynd.xlsx
+++ b/artfynd/A 32783-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149425</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149423</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149422</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149421</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149424</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,8 +1445,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149426</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>